--- a/QCM1_SVT.xlsx
+++ b/QCM1_SVT.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC27372B-8BE4-4C27-81AB-3A2E7874E812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02361B9D-869E-4277-B828-B6912DC320FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{F43DED4A-C9F1-454A-90AB-F65E9F695DB6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil2" sheetId="3" r:id="rId1"/>
+    <sheet name="QCM_Muscle" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>

--- a/QCM1_SVT.xlsx
+++ b/QCM1_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02361B9D-869E-4277-B828-B6912DC320FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17AE7C8-B8DC-4BAF-9AEC-A40630949B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{F43DED4A-C9F1-454A-90AB-F65E9F695DB6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="152">
   <si>
     <t>Question</t>
   </si>
@@ -478,6 +478,9 @@
   </si>
   <si>
     <t xml:space="preserve">Les protéines qui permettent le passage des ions $\text{H}^+$ à travers la membrane mitochondriale sont appelées : </t>
+  </si>
+  <si>
+    <t>Image</t>
   </si>
 </sst>
 </file>
@@ -993,7 +996,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1005,6 +1008,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1382,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C72C8F2-D5CB-4992-A24D-11780BA562E7}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="30.42578125" customWidth="1"/>
@@ -1390,10 +1396,10 @@
     <col min="5" max="5" width="31.7109375" customWidth="1"/>
     <col min="6" max="6" width="34.42578125" customWidth="1"/>
     <col min="7" max="7" width="38.85546875" customWidth="1"/>
-    <col min="8" max="8" width="30.5703125" customWidth="1"/>
+    <col min="8" max="9" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>140</v>
       </c>
@@ -1418,11 +1424,14 @@
       <c r="H1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>149</v>
       </c>
@@ -1447,8 +1456,9 @@
       <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>149</v>
       </c>
@@ -1473,8 +1483,9 @@
       <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>149</v>
       </c>
@@ -1499,8 +1510,9 @@
       <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>149</v>
       </c>
@@ -1525,8 +1537,9 @@
       <c r="H5" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>149</v>
       </c>
@@ -1551,8 +1564,9 @@
       <c r="H6" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>149</v>
       </c>
@@ -1577,8 +1591,9 @@
       <c r="H7" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>149</v>
       </c>
@@ -1603,8 +1618,9 @@
       <c r="H8" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>149</v>
       </c>
@@ -1629,8 +1645,9 @@
       <c r="H9" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>149</v>
       </c>
@@ -1655,8 +1672,9 @@
       <c r="H10" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>149</v>
       </c>
@@ -1681,8 +1699,9 @@
       <c r="H11" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>149</v>
       </c>
@@ -1707,8 +1726,9 @@
       <c r="H12" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>149</v>
       </c>
@@ -1733,8 +1753,9 @@
       <c r="H13" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>149</v>
       </c>
@@ -1759,8 +1780,9 @@
       <c r="H14" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
@@ -1785,8 +1807,9 @@
       <c r="H15" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="72" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>149</v>
       </c>
@@ -1811,8 +1834,9 @@
       <c r="H16" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>149</v>
       </c>
@@ -1837,8 +1861,9 @@
       <c r="H17" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>149</v>
       </c>
@@ -1863,8 +1888,9 @@
       <c r="H18" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>149</v>
       </c>
@@ -1889,8 +1915,9 @@
       <c r="H19" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>149</v>
       </c>
@@ -1915,8 +1942,9 @@
       <c r="H20" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>149</v>
       </c>
@@ -1941,8 +1969,9 @@
       <c r="H21" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>149</v>
       </c>
@@ -1967,8 +1996,9 @@
       <c r="H22" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>149</v>
       </c>
@@ -1993,8 +2023,9 @@
       <c r="H23" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -2019,8 +2050,9 @@
       <c r="H24" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>149</v>
       </c>
@@ -2045,8 +2077,9 @@
       <c r="H25" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>149</v>
       </c>
@@ -2071,8 +2104,9 @@
       <c r="H26" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>149</v>
       </c>
@@ -2097,8 +2131,9 @@
       <c r="H27" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>149</v>
       </c>
@@ -2123,8 +2158,9 @@
       <c r="H28" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>149</v>
       </c>
@@ -2149,8 +2185,9 @@
       <c r="H29" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>149</v>
       </c>
@@ -2175,8 +2212,9 @@
       <c r="H30" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>149</v>
       </c>
@@ -2201,6 +2239,7 @@
       <c r="H31" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="I31" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QCM1_SVT.xlsx
+++ b/QCM1_SVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17AE7C8-B8DC-4BAF-9AEC-A40630949B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB24008D-2188-47FA-A3BD-E4637BCF6ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{F43DED4A-C9F1-454A-90AB-F65E9F695DB6}"/>
   </bookViews>
@@ -474,13 +474,13 @@
     <t>Explication</t>
   </si>
   <si>
-    <t>QCM Chapitre 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Les protéines qui permettent le passage des ions $\text{H}^+$ à travers la membrane mitochondriale sont appelées : </t>
   </si>
   <si>
     <t>Image</t>
+  </si>
+  <si>
+    <t>TEST : Les réactions responsables de la libération de l'énergie emmaagasinée dans la matière organique</t>
   </si>
 </sst>
 </file>
@@ -1425,15 +1425,15 @@
         <v>145</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -1458,9 +1458,9 @@
       </c>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -1485,9 +1485,9 @@
       </c>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -1512,9 +1512,9 @@
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -1539,9 +1539,9 @@
       </c>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>21</v>
@@ -1566,9 +1566,9 @@
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
@@ -1593,9 +1593,9 @@
       </c>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>31</v>
@@ -1620,9 +1620,9 @@
       </c>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -1647,9 +1647,9 @@
       </c>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>41</v>
@@ -1674,9 +1674,9 @@
       </c>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>46</v>
@@ -1701,9 +1701,9 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>51</v>
@@ -1728,9 +1728,9 @@
       </c>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>56</v>
@@ -1755,9 +1755,9 @@
       </c>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>61</v>
@@ -1782,9 +1782,9 @@
       </c>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>66</v>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:10" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>147</v>
@@ -1836,9 +1836,9 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>75</v>
@@ -1863,9 +1863,9 @@
       </c>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>80</v>
@@ -1890,9 +1890,9 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>84</v>
@@ -1917,9 +1917,9 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>89</v>
@@ -1944,9 +1944,9 @@
       </c>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>94</v>
@@ -1971,9 +1971,9 @@
       </c>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>99</v>
@@ -1998,9 +1998,9 @@
       </c>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>104</v>
@@ -2025,9 +2025,9 @@
       </c>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>109</v>
@@ -2052,9 +2052,9 @@
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>114</v>
@@ -2079,9 +2079,9 @@
       </c>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>119</v>
@@ -2106,9 +2106,9 @@
       </c>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>56</v>
@@ -2133,9 +2133,9 @@
       </c>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>128</v>
@@ -2160,9 +2160,9 @@
       </c>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>133</v>
@@ -2187,9 +2187,9 @@
       </c>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>138</v>
@@ -2214,9 +2214,9 @@
       </c>
       <c r="I30" s="5"/>
     </row>
-    <row r="31" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>139</v>
